--- a/Systeme electric/MOQ SystemElectric.xlsx
+++ b/Systeme electric/MOQ SystemElectric.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.13\од\Кейсы для Хакатона\Systeme electric\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\githack\hack-95b86b43-team\Systeme electric\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DFAE80-C760-4ED0-8919-4BEB9C747E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359860A5-809E-4661-84A3-F0B0325E51F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E3090BC-2B6C-4DA6-8DDC-A203E70816B0}"/>
+    <workbookView xWindow="1044" yWindow="1044" windowWidth="17280" windowHeight="10500" xr2:uid="{0E3090BC-2B6C-4DA6-8DDC-A203E70816B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист_1" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -5144,9 +5141,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5184,7 +5181,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5290,7 +5287,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5432,7 +5429,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5445,16 +5442,16 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E557"/>
-  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="11.4" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="74.6640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17.1640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="8.1640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="74.7109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>1658</v>
       </c>
@@ -5471,7 +5468,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -14896,14 +14893,17 @@
         <v>900</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:5" ht="12.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A557" s="2"/>
       <c r="B557" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C557" s="8"/>
       <c r="D557" s="2"/>
-      <c r="E557" s="2"/>
+      <c r="E557" s="2">
+        <f>SUM(E3:E556)</f>
+        <v>14490</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:E557" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
